--- a/config/auto_configs/2020_Hyundai_Hyundai_Elantra(CN7)_G 1.6 T-GDI GAMMA2.xlsx
+++ b/config/auto_configs/2020_Hyundai_Hyundai_Elantra(CN7)_G 1.6 T-GDI GAMMA2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D172"/>
+  <dimension ref="A1:D437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B132600</t>
+          <t>P000A00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -542,17 +542,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B132700</t>
+          <t>P000B00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -564,17 +564,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B132800</t>
+          <t>P001100</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -586,17 +586,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B132900</t>
+          <t>P001400</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B133000</t>
+          <t>P001600</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -630,17 +630,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B133100</t>
+          <t>P003000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,17 +652,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B133200</t>
+          <t>P003100</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -674,17 +674,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B133300</t>
+          <t>P003200</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -696,17 +696,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B133400</t>
+          <t>P003300</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -718,17 +718,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B133500</t>
+          <t>P003400</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -740,17 +740,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B134600</t>
+          <t>P003500</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -762,17 +762,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B134700</t>
+          <t>P003600</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,17 +784,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B134800</t>
+          <t>P003700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -806,17 +806,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B134900</t>
+          <t>P003800</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -828,17 +828,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B135200</t>
+          <t>P003A00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -850,17 +850,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B135300</t>
+          <t>P004500</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -872,17 +872,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B135400</t>
+          <t>P006800</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -894,17 +894,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B135500</t>
+          <t>P007000</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -916,17 +916,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B136100</t>
+          <t>P007100</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -938,17 +938,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B136200</t>
+          <t>P007500</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -960,17 +960,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B136300</t>
+          <t>P007600</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -982,17 +982,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B136400</t>
+          <t>P007700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1004,17 +1004,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B136700</t>
+          <t>P007800</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1026,17 +1026,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B136800</t>
+          <t>P007900</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1048,17 +1048,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B136900</t>
+          <t>P008000</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1070,17 +1070,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B137000</t>
+          <t>P008700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1092,17 +1092,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B137800</t>
+          <t>P008800</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1114,17 +1114,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B137900</t>
+          <t>P008B00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1136,17 +1136,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B138000</t>
+          <t>P009000</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1158,17 +1158,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B138100</t>
+          <t>P00CE00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1180,17 +1180,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B138200</t>
+          <t>P00D100</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1202,17 +1202,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B138300</t>
+          <t>P00D200</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1224,17 +1224,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B138400</t>
+          <t>P010600</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1246,17 +1246,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B138500</t>
+          <t>P010700</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1268,17 +1268,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B140000</t>
+          <t>P010800</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1290,17 +1290,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B140100</t>
+          <t>P011100</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1312,17 +1312,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B140200</t>
+          <t>P011200</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1334,17 +1334,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B140300</t>
+          <t>P011300</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1356,17 +1356,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B140400</t>
+          <t>P011400</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1378,17 +1378,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B140500</t>
+          <t>P011600</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1400,17 +1400,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B140900</t>
+          <t>P011700</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1422,17 +1422,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B141000</t>
+          <t>P011800</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1444,17 +1444,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B141400</t>
+          <t>P011900</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1466,17 +1466,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B141500</t>
+          <t>P011B00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1488,17 +1488,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B147300</t>
+          <t>P012100</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1510,17 +1510,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B147400</t>
+          <t>P012200</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1532,17 +1532,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B147500</t>
+          <t>P012300</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1554,17 +1554,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B147600</t>
+          <t>P012700</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1576,17 +1576,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B147700</t>
+          <t>P013000</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1598,17 +1598,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B147800</t>
+          <t>P013100</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1620,17 +1620,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B147900</t>
+          <t>P013200</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1642,17 +1642,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B148000</t>
+          <t>P013300</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1664,17 +1664,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B148100</t>
+          <t>P013400</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1686,17 +1686,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B148200</t>
+          <t>P013500</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1708,17 +1708,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B148300</t>
+          <t>P013600</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1730,17 +1730,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B148400</t>
+          <t>P013700</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1752,17 +1752,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B148500</t>
+          <t>P013800</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1774,17 +1774,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B148600</t>
+          <t>P013A00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1796,17 +1796,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B148700</t>
+          <t>P013B00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1818,17 +1818,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B148800</t>
+          <t>P013E00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1840,17 +1840,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B149000</t>
+          <t>P013F00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1862,17 +1862,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B149300</t>
+          <t>P019200</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1884,17 +1884,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B149400</t>
+          <t>P019300</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1906,17 +1906,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B151100</t>
+          <t>P019600</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1928,17 +1928,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B151200</t>
+          <t>P019700</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1950,17 +1950,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B151300</t>
+          <t>P019800</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1972,17 +1972,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B151400</t>
+          <t>P020100</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1994,17 +1994,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B151500</t>
+          <t>P020200</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2016,17 +2016,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B151600</t>
+          <t>P020300</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2038,17 +2038,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B162000</t>
+          <t>P020400</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2060,17 +2060,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B165000</t>
+          <t>P022100</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2082,17 +2082,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B165100</t>
+          <t>P022200</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2104,17 +2104,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B165200</t>
+          <t>P022300</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2126,17 +2126,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B165800</t>
+          <t>P023400</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2148,17 +2148,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B167000</t>
+          <t>P026100</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2170,17 +2170,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B167600</t>
+          <t>P026200</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2192,17 +2192,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B167700</t>
+          <t>P026400</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2214,17 +2214,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B167800</t>
+          <t>P026500</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2236,17 +2236,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B168400</t>
+          <t>P026700</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2258,17 +2258,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B16D200</t>
+          <t>P026800</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2280,17 +2280,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B16D300</t>
+          <t>P027000</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2302,17 +2302,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B173800</t>
+          <t>P027100</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2324,17 +2324,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B173900</t>
+          <t>P029900</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2346,17 +2346,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B174000</t>
+          <t>P030100</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2368,17 +2368,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B174100</t>
+          <t>P030200</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2390,17 +2390,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B174200</t>
+          <t>P030300</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2412,17 +2412,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B174400</t>
+          <t>P030400</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2434,17 +2434,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B174500</t>
+          <t>P032600</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2456,17 +2456,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B174600</t>
+          <t>P033500</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2478,17 +2478,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B174700</t>
+          <t>P033600</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2500,17 +2500,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B174800</t>
+          <t>P034100</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2522,17 +2522,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B176200</t>
+          <t>P034200</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2544,17 +2544,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B204000</t>
+          <t>P034300</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2566,17 +2566,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B204100</t>
+          <t>P036600</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2588,17 +2588,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B204200</t>
+          <t>P036700</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2610,17 +2610,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B204300</t>
+          <t>P036800</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2632,17 +2632,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B250200</t>
+          <t>P044200</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2654,17 +2654,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B261300</t>
+          <t>P044400</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2676,17 +2676,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B261500</t>
+          <t>P044900</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2698,17 +2698,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>HMA_HK_00106</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B261600</t>
+          <t>P045100</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2720,17 +2720,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>C110913</t>
+          <t>P045200</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2742,17 +2742,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>C120001</t>
+          <t>P045300</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2764,17 +2764,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>C120102</t>
+          <t>P045500</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2786,17 +2786,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>C120202</t>
+          <t>P045600</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2808,17 +2808,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>C120301</t>
+          <t>P045800</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2830,17 +2830,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>C120402</t>
+          <t>P045900</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2852,17 +2852,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>C120502</t>
+          <t>P046200</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2874,17 +2874,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>C120601</t>
+          <t>P046300</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2896,17 +2896,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>C120702</t>
+          <t>P049800</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2918,17 +2918,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>C120802</t>
+          <t>P049900</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2940,17 +2940,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>C120901</t>
+          <t>P04DF00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2962,17 +2962,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>C121002</t>
+          <t>P04E000</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2984,17 +2984,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>C121102</t>
+          <t>P050400</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3006,17 +3006,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>C123501</t>
+          <t>P050600</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3028,17 +3028,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>C126002</t>
+          <t>P050700</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3050,17 +3050,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>C126104</t>
+          <t>P050A00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3072,17 +3072,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>C126402</t>
+          <t>P050C00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3094,17 +3094,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>C128302</t>
+          <t>P053200</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3116,17 +3116,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>C128504</t>
+          <t>P053300</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3138,17 +3138,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>C128602</t>
+          <t>P05CC00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3160,17 +3160,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>C135801</t>
+          <t>P05CE00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3182,17 +3182,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>C150301</t>
+          <t>P060500</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3204,17 +3204,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>C152701</t>
+          <t>P062000</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3226,17 +3226,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>C161108</t>
+          <t>P063000</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3248,17 +3248,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>C161208</t>
+          <t>P063800</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3270,17 +3270,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>C161B08</t>
+          <t>P064200</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3292,17 +3292,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>C162308</t>
+          <t>P064300</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3314,17 +3314,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>C162808</t>
+          <t>P064A00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3336,17 +3336,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>C162A87</t>
+          <t>P064D00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3358,17 +3358,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>C163808</t>
+          <t>P123000</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3380,17 +3380,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>C164308</t>
+          <t>P193100</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3402,17 +3402,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>C164908</t>
+          <t>P193300</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3424,17 +3424,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>C165008</t>
+          <t>P193600</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3446,17 +3446,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>C168708</t>
+          <t>P193700</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3468,17 +3468,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>C168808</t>
+          <t>P193B00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3490,17 +3490,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>C16B687</t>
+          <t>P193C00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3512,17 +3512,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>C16B781</t>
+          <t>P212200</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3534,17 +3534,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>C171055</t>
+          <t>P212300</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3556,17 +3556,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>C181208</t>
+          <t>P212700</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3578,17 +3578,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>C181708</t>
+          <t>P212800</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3600,17 +3600,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>C181887</t>
+          <t>P213800</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3622,17 +3622,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>C183786</t>
+          <t>P215900</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3644,17 +3644,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>C184786</t>
+          <t>P218300</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3666,17 +3666,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>C184787</t>
+          <t>P218400</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3688,17 +3688,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>C220277</t>
+          <t>P218500</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3710,17 +3710,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>C222001</t>
+          <t>P218600</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3732,17 +3732,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>C222071</t>
+          <t>P219500</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -3754,17 +3754,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>C222074</t>
+          <t>P219600</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3776,17 +3776,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>C222077</t>
+          <t>P219C00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -3798,17 +3798,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>C222094</t>
+          <t>P219D00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3820,17 +3820,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>C222401</t>
+          <t>P219E00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3842,17 +3842,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>C222471</t>
+          <t>P219F00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3864,17 +3864,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>C222474</t>
+          <t>P222800</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3886,17 +3886,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>C222477</t>
+          <t>P222900</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3908,17 +3908,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>C222494</t>
+          <t>P223700</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3930,17 +3930,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>C224077</t>
+          <t>P224300</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -3952,17 +3952,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>C224494</t>
+          <t>P225100</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -3974,17 +3974,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>C238001</t>
+          <t>P226100</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -3996,17 +3996,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>C240201</t>
+          <t>P227000</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4018,17 +4018,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>C241601</t>
+          <t>P227100</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4040,17 +4040,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>C241611</t>
+          <t>P241400</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4062,17 +4062,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>C241612</t>
+          <t>P242200</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4084,17 +4084,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>C241613</t>
+          <t>P250100</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4106,17 +4106,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>C241671</t>
+          <t>P254000</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4128,17 +4128,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>C241701</t>
+          <t>P254100</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4150,17 +4150,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>C241711</t>
+          <t>P254200</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4172,17 +4172,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>C241712</t>
+          <t>P262600</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4194,17 +4194,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>C241713</t>
+          <t>U000100</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4216,17 +4216,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>C241771</t>
+          <t>U010100</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -4238,17 +4238,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>HMA_HK_00105</t>
+          <t>HMA_HK_00103</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>C241877</t>
+          <t>U012100</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -4260,20 +4260,5850 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>P060147</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>P06B311</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>P070529</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>P070564</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>P071512</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>P071514</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>P071603</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>P071631</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>P073E07</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>P073E71</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>P073E73</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>P073E77</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>P073F07</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>P073F71</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>P073F73</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>P073F77</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>P074A07</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>P074A71</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>P074A73</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>P074A77</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>P074B07</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>P074B71</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>P074B73</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>P074B77</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>P074C07</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>P074C71</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>P074C73</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>P074C77</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>P074D07</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>P074D71</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>P074D73</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>P074D77</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>P074E07</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>P074E71</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>P074E73</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>P074E77</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>P074F07</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>P074F71</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>P074F73</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>P074F77</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>P082008</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>P082016</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>P082017</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>P090173</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>P090B73</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>P091011</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>P091012</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>P091013</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>P091015</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>P092177</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>P092198</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>P095529</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>P17C000</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>P191011</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>P191012</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>P191013</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>P191015</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>P192177</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>P192198</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>P276512</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>P276514</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>P276603</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>P276631</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>U000188</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>U005586</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>U006487</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>U010087</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>U012187</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>U110087</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>U110341</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>HMA_HK_00104</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>U111788</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
           <t>ABS/ESC</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B243" t="inlineStr">
         <is>
           <t>HMA_HK_00105</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>C110913</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>C120001</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>C120102</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>C120202</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>C120301</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>C120402</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>C120502</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>C120601</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>C120702</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>C120802</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>C120901</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>C121002</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>C121102</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>C123501</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>C126002</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>C126104</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>C126402</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>C128302</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>C128504</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>C128602</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>C135801</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>C150301</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>C152701</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>C161108</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>C161208</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>C161B08</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>C162308</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>C162808</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>C162A87</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>C163808</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>C164308</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>C164908</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>C165008</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>C168708</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>C168808</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>C16B687</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>C16B781</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>C171055</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>C181208</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>C181708</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>C181887</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>C183786</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>C184786</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>C184787</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>C220277</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>C222001</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>C222071</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>C222074</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>C222077</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>C222094</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>C222401</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>C222471</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>C222474</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>C222477</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>C222494</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>C224077</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>C224494</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>C238001</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>C240201</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>C241601</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>C241611</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>C241612</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>C241613</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>C241671</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>C241701</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>C241711</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>C241712</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>C241713</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>C241771</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>C241877</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>HMA_HK_00105</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
         <is>
           <t>C241977</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>B132600</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>B132700</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>B132800</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>B132900</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>B133000</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>B133100</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>B133200</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>B133300</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>B133400</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>B133500</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>B134600</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>B134700</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>B134800</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>B134900</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>B135200</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>B135300</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>B135400</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>B135500</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>B136100</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>B136200</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>B136300</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>B136400</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>B136700</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>B136800</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>B136900</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>B137000</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>B137800</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>B137900</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>B138000</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>B138100</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>B138200</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>B138300</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>B138400</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>B138500</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>B140000</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>B140100</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>B140200</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>B140300</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>B140400</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>B140500</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>B140900</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>B141000</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>B141400</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>B141500</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>B147300</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>B147400</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>B147500</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>B147600</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>B147700</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>B147800</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>B147900</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>B148000</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>B148100</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>B148200</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>B148300</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>B148400</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>B148500</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>B148600</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>B148700</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>B148800</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>B149000</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>B149300</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>B149400</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>B151100</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>B151200</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>B151300</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>B151400</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>B151500</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>B151600</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>B162000</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>B165000</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>B165100</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>B165200</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>B165800</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>B167000</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>B167600</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>B167700</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>B167800</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>B168400</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>B16D200</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>B16D300</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>B173800</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>B173900</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>B174000</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>B174100</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>B174200</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>B174400</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>B174500</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>B174600</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>B174700</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>B174800</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>B176200</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>B204000</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>B204100</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>B204200</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>B204300</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>B250200</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>B261300</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>B261500</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>HMA_HK_00106</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>B261600</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>IBU-TPMS</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>HMA_HK_00108</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>HMA_HK_00109</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>ADAS_P</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>HMA_HK_00110</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>HMA_HK_00111</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>AVN</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>HMA_HK_00112</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>CLU</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>HMA_HK_00113</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>HMA_HK_00172</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>HMA_HK_00115</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>FVC</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>HMA_HK_00116</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>IAU</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>HMA_HK_00117</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>IBU-BCM</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>HMA_HK_00118</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>IBU-IMM</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>HMA_HK_00119</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>IBU-SKU</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>HMA_HK_00120</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>ICU</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>HMA_HK_00121</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>MLM</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>HMA_HK_00122</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>ODS</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>HMA_HK_00123</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>PSM</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>HMA_HK_00124</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>RCR_L</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>HMA_HK_00125</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>RCR_R</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>HMA_HK_00126</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>RVMS</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>HMA_HK_00127</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>SHVU-F</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>HMA_HK_00128</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>SHVU-R</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>HMA_HK_00129</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>T-CS</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>HMA_HK_00130</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>WPC</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>HMA_HK_00131</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
         <is>
           <t>00</t>
         </is>
